--- a/artfynd/A 15011-2025 artfynd.xlsx
+++ b/artfynd/A 15011-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125632798</v>
       </c>
       <c r="B2" t="n">
-        <v>105348</v>
+        <v>105355</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 15011-2025 artfynd.xlsx
+++ b/artfynd/A 15011-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125632798</v>
       </c>
       <c r="B2" t="n">
-        <v>105355</v>
+        <v>105358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 15011-2025 artfynd.xlsx
+++ b/artfynd/A 15011-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125632798</v>
       </c>
       <c r="B2" t="n">
-        <v>105358</v>
+        <v>105362</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 15011-2025 artfynd.xlsx
+++ b/artfynd/A 15011-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125632798</v>
       </c>
       <c r="B2" t="n">
-        <v>105362</v>
+        <v>105363</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 15011-2025 artfynd.xlsx
+++ b/artfynd/A 15011-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125632798</v>
       </c>
       <c r="B2" t="n">
-        <v>105363</v>
+        <v>105365</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 15011-2025 artfynd.xlsx
+++ b/artfynd/A 15011-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125632798</v>
       </c>
       <c r="B2" t="n">
-        <v>105365</v>
+        <v>105367</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 15011-2025 artfynd.xlsx
+++ b/artfynd/A 15011-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125632798</v>
       </c>
       <c r="B2" t="n">
-        <v>105367</v>
+        <v>105371</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 15011-2025 artfynd.xlsx
+++ b/artfynd/A 15011-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125632798</v>
       </c>
       <c r="B2" t="n">
-        <v>105371</v>
+        <v>105384</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
